--- a/locais.xlsx
+++ b/locais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arman\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517A62CB-CA1E-49FF-A7FF-F5C7155A1BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E329076-28C5-4237-8A5F-137028BAF7BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="255">
   <si>
     <t>categoria</t>
   </si>
@@ -761,6 +761,147 @@
   </si>
   <si>
     <t>Loja LEGO</t>
+  </si>
+  <si>
+    <t>Castelo de Amboise</t>
+  </si>
+  <si>
+    <t>Sculpture de l'émir Abdelkader</t>
+  </si>
+  <si>
+    <t>1 Quai du Général de Gaulle, 37400 Amboise, França</t>
+  </si>
+  <si>
+    <t>Castelo gótico e renascentista do século XV, com salas repletas de tapeçarias e terraço panorâmico.</t>
+  </si>
+  <si>
+    <t>Mnt de l'Emir Abd el Kader, 37400 Amboise, França</t>
+  </si>
+  <si>
+    <t>chateau</t>
+  </si>
+  <si>
+    <t>Tomb of Leonardo da Vinci</t>
+  </si>
+  <si>
+    <t>15 Rue de la Concorde, 37400 Amboise, França</t>
+  </si>
+  <si>
+    <t>Panorama sur la Ville d'Amboise</t>
+  </si>
+  <si>
+    <t>Statue Leonardo da Vinci</t>
+  </si>
+  <si>
+    <t>10 Quai François Tissard, 37400 Amboise, França</t>
+  </si>
+  <si>
+    <t>Chateau d'Amboise viewpoint</t>
+  </si>
+  <si>
+    <t>10-4 Quai François Tissard, 37400 Amboise, França</t>
+  </si>
+  <si>
+    <t>9 Quai François Tissard, 37400 Amboise, França</t>
+  </si>
+  <si>
+    <t>5 Quai du Général de Gaulle, 37400 Amboise, França</t>
+  </si>
+  <si>
+    <t>Netto Amboise</t>
+  </si>
+  <si>
+    <t>21 Av. de Tours, 37400 Amboise, França</t>
+  </si>
+  <si>
+    <t>Crêperie Les 4 saisons</t>
+  </si>
+  <si>
+    <t>44 Pl. Michel Debré, 37400 Amboise, França</t>
+  </si>
+  <si>
+    <t>Horário: 11:40–21:30</t>
+  </si>
+  <si>
+    <t>Capela de Saint-Hubert</t>
+  </si>
+  <si>
+    <t>Emir Abdel-Kader, Château Royal d'Amboise Montée de l, 15 Rue de la Concorde, 37400 Amboise, França</t>
+  </si>
+  <si>
+    <t>Amorino</t>
+  </si>
+  <si>
+    <t>Horário: 12:00–21:45</t>
+  </si>
+  <si>
+    <t>6 Pl. Michel Debré, 37400 Amboise, França</t>
+  </si>
+  <si>
+    <t>Carrefour Contact</t>
+  </si>
+  <si>
+    <t>44 Rue Grégoire de Tours, 37400 Amboise, França</t>
+  </si>
+  <si>
+    <t>L'Ile d'Or</t>
+  </si>
+  <si>
+    <t>2 Pl. Saint-Roch, 37400 Amboise, França</t>
+  </si>
+  <si>
+    <t>Pequeno museu na antiga casa de Da Vinci em cujos terrenos estão expostos modelos funcionais das suas invenções.</t>
+  </si>
+  <si>
+    <t>2 Rue du Clos Lucé, 37400 Amboise, França</t>
+  </si>
+  <si>
+    <t>Château Du Clos Lucé</t>
+  </si>
+  <si>
+    <t>Château Gaillard</t>
+  </si>
+  <si>
+    <t>29 All. du Pont Moulin, 37400 Amboise, França</t>
+  </si>
+  <si>
+    <t>Tour de l'Horloge</t>
+  </si>
+  <si>
+    <t>7 Rue nationale 3, 37400 Amboise, França</t>
+  </si>
+  <si>
+    <t>Built in the 15th century and listed as a Monument Historique since 1933, the Tour de l'horloge is at the heart of Amboise's historic center. This impressive medieval tower once served as the town's main gateway, forming part of its fortifications. We particularly liked its sleek silhouette and reassuring presence on the city streets. Finally, you can discover other elegant and picturesque facades as you stroll through the historic center.</t>
+  </si>
+  <si>
+    <t>Amboise Train Station</t>
+  </si>
+  <si>
+    <t>37400 Amboise, França</t>
+  </si>
+  <si>
+    <t>Intermarché SUPER Pocé Sur Cisse</t>
+  </si>
+  <si>
+    <t>Boulevard du sevrage, La Ramée, 37530 Pocé-sur-Cisse, França</t>
+  </si>
+  <si>
+    <t>Château de Chenonceau</t>
+  </si>
+  <si>
+    <t>37150 Chenonceaux, França</t>
+  </si>
+  <si>
+    <t>Castelo imponente do século XVII sobre o rio com tapeçaria e coleção de quadros de antigos mestres.</t>
+  </si>
+  <si>
+    <t>Chenonceaux train Station</t>
+  </si>
+  <si>
+    <t>47.´,33120753501752</t>
+  </si>
+  <si>
+    <t>37150 Chisseaux, França</t>
   </si>
 </sst>
 </file>
@@ -832,7 +973,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -846,6 +987,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1061,7 +1205,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J927"/>
+  <dimension ref="A1:J926"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.44140625" style="2" customWidth="1"/>
@@ -2035,49 +2179,49 @@
       </c>
     </row>
     <row r="43" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="4" t="s">
-        <v>60</v>
+      <c r="A43" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>57</v>
+        <v>135</v>
       </c>
       <c r="C43" s="2">
-        <v>47.386096099574097</v>
+        <v>48.726014490487898</v>
       </c>
       <c r="D43" s="2">
-        <v>0.68337313544856004</v>
+        <v>2.26138776454144</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>58</v>
+        <v>136</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>34</v>
+        <v>137</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>119</v>
+      <c r="A44" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C44" s="2">
-        <v>48.726014490487898</v>
+        <v>48.858513981162801</v>
       </c>
       <c r="D44" s="2">
-        <v>2.26138776454144</v>
+        <v>2.2945633786699</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>146</v>
@@ -2088,68 +2232,68 @@
         <v>61</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C45" s="2">
-        <v>48.858513981162801</v>
+        <v>48.853204736689797</v>
       </c>
       <c r="D45" s="2">
-        <v>2.2945633786699</v>
+        <v>2.3498919294168501</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="4" t="s">
-        <v>61</v>
+      <c r="A46" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C46" s="2">
-        <v>48.853204736689797</v>
+        <v>48.842213649455601</v>
       </c>
       <c r="D46" s="2">
-        <v>2.3498919294168501</v>
+        <v>2.3679672585834699</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>139</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>119</v>
+      <c r="A47" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C47" s="2">
-        <v>48.842213649455601</v>
+        <v>48.861080067252502</v>
       </c>
       <c r="D47" s="2">
-        <v>2.3679672585834699</v>
+        <v>2.3375270598039402</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>146</v>
@@ -2160,19 +2304,22 @@
         <v>61</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C48" s="2">
-        <v>48.861080067252502</v>
+        <v>48.871902733098203</v>
       </c>
       <c r="D48" s="2">
-        <v>2.3375270598039402</v>
+        <v>2.3337470974475298</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>146</v>
@@ -2183,22 +2330,19 @@
         <v>61</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C49" s="2">
-        <v>48.871902733098203</v>
+        <v>48.875176996242899</v>
       </c>
       <c r="D49" s="2">
-        <v>2.3337470974475298</v>
+        <v>2.2950372327420898</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>146</v>
@@ -2209,19 +2353,19 @@
         <v>61</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C50" s="2">
-        <v>48.875176996242899</v>
+        <v>48.866828089800201</v>
       </c>
       <c r="D50" s="2">
-        <v>2.2950372327420898</v>
+        <v>2.3101717088609202</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>146</v>
@@ -2232,19 +2376,19 @@
         <v>61</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C51" s="2">
-        <v>48.866828089800201</v>
+        <v>48.864156282808601</v>
       </c>
       <c r="D51" s="2">
-        <v>2.3101717088609202</v>
+        <v>2.2875711928928202</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>146</v>
@@ -2255,19 +2399,19 @@
         <v>61</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C52" s="2">
-        <v>48.864156282808601</v>
+        <v>48.866438356943803</v>
       </c>
       <c r="D52" s="2">
-        <v>2.2875711928928202</v>
+        <v>2.3210612158246899</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>146</v>
@@ -2275,22 +2419,25 @@
     </row>
     <row r="53" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>157</v>
+        <v>90</v>
       </c>
       <c r="C53" s="2">
-        <v>48.866438356943803</v>
+        <v>48.861923891092502</v>
       </c>
       <c r="D53" s="2">
-        <v>2.3210612158246899</v>
+        <v>2.3533037596324502</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>159</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>146</v>
@@ -2304,16 +2451,16 @@
         <v>90</v>
       </c>
       <c r="C54" s="2">
-        <v>48.861923891092502</v>
+        <v>48.867693321962697</v>
       </c>
       <c r="D54" s="2">
-        <v>2.3533037596324502</v>
+        <v>2.3366026191593101</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>92</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>159</v>
@@ -2327,22 +2474,22 @@
         <v>91</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="C55" s="2">
-        <v>48.867693321962697</v>
+        <v>48.8678075061908</v>
       </c>
       <c r="D55" s="2">
-        <v>2.3366026191593101</v>
+        <v>2.3319670236838399</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>92</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>159</v>
+        <v>93</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>146</v>
@@ -2353,22 +2500,22 @@
         <v>91</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="C56" s="2">
-        <v>48.8678075061908</v>
+        <v>48.8721353475946</v>
       </c>
       <c r="D56" s="2">
-        <v>2.3319670236838399</v>
+        <v>2.3277995704002898</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>92</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>93</v>
+        <v>159</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>146</v>
@@ -2382,19 +2529,19 @@
         <v>90</v>
       </c>
       <c r="C57" s="2">
-        <v>48.8721353475946</v>
+        <v>48.872009844263502</v>
       </c>
       <c r="D57" s="2">
-        <v>2.3277995704002898</v>
+        <v>2.30787645038777</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>92</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>159</v>
+        <v>93</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>146</v>
@@ -2408,19 +2555,19 @@
         <v>90</v>
       </c>
       <c r="C58" s="2">
-        <v>48.872009844263502</v>
+        <v>48.867396991537497</v>
       </c>
       <c r="D58" s="2">
-        <v>2.30787645038777</v>
+        <v>2.28830365259968</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>92</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>93</v>
+        <v>159</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>146</v>
@@ -2434,16 +2581,16 @@
         <v>90</v>
       </c>
       <c r="C59" s="2">
-        <v>48.867396991537497</v>
+        <v>48.855288505275198</v>
       </c>
       <c r="D59" s="2">
-        <v>2.28830365259968</v>
+        <v>2.30605725799419</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>92</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>159</v>
@@ -2460,16 +2607,16 @@
         <v>90</v>
       </c>
       <c r="C60" s="2">
-        <v>48.855288505275198</v>
+        <v>48.860455292791301</v>
       </c>
       <c r="D60" s="2">
-        <v>2.30605725799419</v>
+        <v>2.3072506450714898</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>92</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>159</v>
@@ -2483,22 +2630,22 @@
         <v>91</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>90</v>
+        <v>168</v>
       </c>
       <c r="C61" s="2">
-        <v>48.860455292791301</v>
+        <v>48.852711938374</v>
       </c>
       <c r="D61" s="2">
-        <v>2.3072506450714898</v>
+        <v>2.3441734492746198</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>92</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>146</v>
@@ -2509,22 +2656,22 @@
         <v>91</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C62" s="2">
-        <v>48.852711938374</v>
+        <v>48.8596015950978</v>
       </c>
       <c r="D62" s="2">
-        <v>2.3441734492746198</v>
+        <v>2.3483370164269601</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>92</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>146</v>
@@ -2535,22 +2682,22 @@
         <v>91</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C63" s="2">
-        <v>48.8596015950978</v>
+        <v>48.855608600911602</v>
       </c>
       <c r="D63" s="2">
-        <v>2.3483370164269601</v>
+        <v>2.3042669005823999</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>92</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>146</v>
@@ -2561,22 +2708,22 @@
         <v>91</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>174</v>
+        <v>123</v>
       </c>
       <c r="C64" s="2">
-        <v>48.855608600911602</v>
+        <v>48.852035662443399</v>
       </c>
       <c r="D64" s="2">
-        <v>2.3042669005823999</v>
+        <v>2.3427284359591898</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>92</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>146</v>
@@ -2590,19 +2737,19 @@
         <v>123</v>
       </c>
       <c r="C65" s="2">
-        <v>48.852035662443399</v>
+        <v>48.867339811936098</v>
       </c>
       <c r="D65" s="2">
-        <v>2.3427284359591898</v>
+        <v>2.3334618056774001</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>92</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>146</v>
@@ -2610,25 +2757,25 @@
     </row>
     <row r="66" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
       <c r="C66" s="2">
-        <v>48.867339811936098</v>
+        <v>48.852786067245603</v>
       </c>
       <c r="D66" s="2">
-        <v>2.3334618056774001</v>
+        <v>2.3442554019082502</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>146</v>
@@ -2639,22 +2786,22 @@
         <v>74</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C67" s="2">
-        <v>48.852786067245603</v>
+        <v>48.853329736877797</v>
       </c>
       <c r="D67" s="2">
-        <v>2.3442554019082502</v>
+        <v>2.3464503920931299</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>146</v>
@@ -2665,22 +2812,22 @@
         <v>74</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C68" s="2">
-        <v>48.853329736877797</v>
+        <v>48.864514704841497</v>
       </c>
       <c r="D68" s="2">
-        <v>2.3464503920931299</v>
+        <v>2.34108268279003</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>146</v>
@@ -2691,48 +2838,48 @@
         <v>74</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C69" s="2">
-        <v>48.864514704841497</v>
+        <v>48.853863109085999</v>
       </c>
       <c r="D69" s="2">
-        <v>2.34108268279003</v>
+        <v>2.29660140784739</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="4" t="s">
-        <v>74</v>
+      <c r="A70" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C70" s="2">
-        <v>48.853863109085999</v>
+        <v>48.854007409440001</v>
       </c>
       <c r="D70" s="2">
-        <v>2.29660140784739</v>
+        <v>2.28921680478263</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>146</v>
@@ -2743,45 +2890,45 @@
         <v>12</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C71" s="2">
-        <v>48.854007409440001</v>
+        <v>48.837061646848603</v>
       </c>
       <c r="D71" s="2">
-        <v>2.28921680478263</v>
+        <v>2.3727742453623901</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>194</v>
+        <v>140</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>12</v>
+      <c r="A72" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C72" s="2">
-        <v>48.837061646848603</v>
+        <v>48.851654440930197</v>
       </c>
       <c r="D72" s="2">
-        <v>2.3727742453623901</v>
+        <v>2.3478139190429101</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>140</v>
+        <v>197</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>198</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>146</v>
@@ -2795,19 +2942,19 @@
         <v>196</v>
       </c>
       <c r="C73" s="2">
-        <v>48.851654440930197</v>
+        <v>48.863964398668401</v>
       </c>
       <c r="D73" s="2">
-        <v>2.3478139190429101</v>
+        <v>2.33442905569505</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>92</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>146</v>
@@ -2821,19 +2968,19 @@
         <v>196</v>
       </c>
       <c r="C74" s="2">
-        <v>48.863964398668401</v>
+        <v>48.871321510497097</v>
       </c>
       <c r="D74" s="2">
-        <v>2.33442905569505</v>
+        <v>2.30420784055993</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>92</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>146</v>
@@ -2847,19 +2994,19 @@
         <v>196</v>
       </c>
       <c r="C75" s="2">
-        <v>48.871321510497097</v>
+        <v>48.855967140591801</v>
       </c>
       <c r="D75" s="2">
-        <v>2.30420784055993</v>
+        <v>2.2949297558487198</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>92</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>146</v>
@@ -2867,22 +3014,22 @@
     </row>
     <row r="76" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
-        <v>91</v>
+        <v>207</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="C76" s="2">
-        <v>48.855967140591801</v>
+        <v>48.8632227508607</v>
       </c>
       <c r="D76" s="2">
-        <v>2.2949297558487198</v>
+        <v>2.3486028944285802</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>92</v>
+        <v>206</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>105</v>
@@ -2893,49 +3040,494 @@
     </row>
     <row r="77" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
-        <v>207</v>
+        <v>61</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C77" s="2">
-        <v>48.8632227508607</v>
+        <v>47.413733507074802</v>
       </c>
       <c r="D77" s="2">
-        <v>2.3486028944285802</v>
+        <v>0.98594731486206499</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>206</v>
+        <v>16</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="G77" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C78" s="2">
+        <v>47.413479424897197</v>
+      </c>
+      <c r="D78" s="2">
+        <v>0.98294323615814505</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C79" s="2">
+        <v>47.4130425327875</v>
+      </c>
+      <c r="D79" s="2">
+        <v>0.98578377184302701</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C80" s="2">
+        <v>47.412886896772697</v>
+      </c>
+      <c r="D80" s="2">
+        <v>0.98895796143744796</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C81" s="2">
+        <v>47.416066544200497</v>
+      </c>
+      <c r="D81" s="2">
+        <v>0.98566689863289103</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C82" s="2">
+        <v>47.415566311623699</v>
+      </c>
+      <c r="D82" s="2">
+        <v>0.98417824869841997</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C83" s="2">
+        <v>47.412791099042799</v>
+      </c>
+      <c r="D83" s="2">
+        <v>0.98253768409319198</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C84" s="2">
+        <v>47.4092478197879</v>
+      </c>
+      <c r="D84" s="2">
+        <v>0.97214814676860695</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C85" s="2">
+        <v>47.412769876346097</v>
+      </c>
+      <c r="D85" s="2">
+        <v>0.98602352224926304</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C86" s="2">
+        <v>47.413125638797503</v>
+      </c>
+      <c r="D86" s="2">
+        <v>0.98576604135895196</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C87" s="2">
+        <v>47.412852491002397</v>
+      </c>
+      <c r="D87" s="2">
+        <v>0.98446642064630596</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C88" s="2">
+        <v>47.405570795842401</v>
+      </c>
+      <c r="D88" s="2">
+        <v>0.98632333684602902</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="G88" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H77" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="79" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="80" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="H88" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C89" s="2">
+        <v>47.415852106154802</v>
+      </c>
+      <c r="D89" s="2">
+        <v>0.98297738159835701</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C90" s="2">
+        <v>47.410377374476901</v>
+      </c>
+      <c r="D90" s="2">
+        <v>0.99213704808260905</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C91" s="2">
+        <v>47.410622891466197</v>
+      </c>
+      <c r="D91" s="2">
+        <v>0.99951817423496403</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C92" s="2">
+        <v>47.413192305998599</v>
+      </c>
+      <c r="D92" s="2">
+        <v>0.98413578832172099</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C93" s="2">
+        <v>47.4219586884481</v>
+      </c>
+      <c r="D93" s="2">
+        <v>0.98114411977988703</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C94" s="2">
+        <v>47.425377841772999</v>
+      </c>
+      <c r="D94" s="2">
+        <v>0.98090807085920295</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C95" s="2">
+        <v>47.325273232451103</v>
+      </c>
+      <c r="D95" s="2">
+        <v>1.06986127937666</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D96" s="2">
+        <v>1.0656132904754301</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
     <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3766,7 +4358,6 @@
     <row r="924" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>

--- a/locais.xlsx
+++ b/locais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arman\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E329076-28C5-4237-8A5F-137028BAF7BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F84DFABD-52C5-4255-AA14-E4323297ACA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="254">
   <si>
     <t>categoria</t>
   </si>
@@ -896,9 +896,6 @@
   </si>
   <si>
     <t>Chenonceaux train Station</t>
-  </si>
-  <si>
-    <t>47.´,33120753501752</t>
   </si>
   <si>
     <t>37150 Chisseaux, França</t>
@@ -973,7 +970,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -990,6 +987,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3512,8 +3510,8 @@
       <c r="B96" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C96" s="2" t="s">
-        <v>253</v>
+      <c r="C96" s="8">
+        <v>47.330920190146998</v>
       </c>
       <c r="D96" s="2">
         <v>1.0656132904754301</v>
@@ -3522,7 +3520,7 @@
         <v>13</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>213</v>

--- a/locais.xlsx
+++ b/locais.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arman\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F84DFABD-52C5-4255-AA14-E4323297ACA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B0DCB26-80F2-4F09-BACC-3592ED4363CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$96</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="259">
   <si>
     <t>categoria</t>
   </si>
@@ -900,11 +903,29 @@
   <si>
     <t>37150 Chisseaux, França</t>
   </si>
+  <si>
+    <t>Sostrene Grene</t>
+  </si>
+  <si>
+    <t>72 Rue Nationale, 37000 Tours, França</t>
+  </si>
+  <si>
+    <t>Horário: Segunda a Sábado,10:00–19:00</t>
+  </si>
+  <si>
+    <t>24 Rue Berger, 75001 Paris, França</t>
+  </si>
+  <si>
+    <t>Horário: 10:00–20:30</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="170" formatCode="#,##0.00000000"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -987,7 +1008,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3526,22 +3547,69 @@
         <v>213</v>
       </c>
     </row>
-    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="97" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C97" s="2">
+        <v>47.393237613937202</v>
+      </c>
+      <c r="D97" s="2">
+        <v>0.68869195670736505</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C98" s="2">
+        <v>48.861846188110803</v>
+      </c>
+      <c r="D98" s="2">
+        <v>2.34700921536915</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="100" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="101" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="102" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="103" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="104" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="105" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="106" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="107" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="108" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="109" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="110" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="111" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="112" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -4357,6 +4425,7 @@
     <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <autoFilter ref="A1:J96" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>

--- a/locais.xlsx
+++ b/locais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arman\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B0DCB26-80F2-4F09-BACC-3592ED4363CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A883B1-82F6-479E-AA67-CC8526350947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="266">
   <si>
     <t>categoria</t>
   </si>
@@ -918,13 +918,34 @@
   <si>
     <t>Horário: 10:00–20:30</t>
   </si>
+  <si>
+    <t>Boutique Aroma-Zone Paris Forum des Halles</t>
+  </si>
+  <si>
+    <t>7 Rue Pierre Lescot, 75001 Paris, França</t>
+  </si>
+  <si>
+    <t>Boutique Aroma-Zone Paris Opéra</t>
+  </si>
+  <si>
+    <t>26 Av. de l'Opéra, 75001 Paris, França</t>
+  </si>
+  <si>
+    <t>Horário: 10:00–20:00</t>
+  </si>
+  <si>
+    <t>Boutique Aroma-Zone Paris Haussmann</t>
+  </si>
+  <si>
+    <t>73 Bd Haussmann, 75008 Paris, França</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="#,##0.00000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00000000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -1008,7 +1029,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3596,9 +3617,84 @@
         <v>146</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="100" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="101" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="99" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C99" s="2">
+        <v>48.862122919056901</v>
+      </c>
+      <c r="D99" s="2">
+        <v>2.3481580288628399</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C100" s="2">
+        <v>48.866996022133499</v>
+      </c>
+      <c r="D100" s="2">
+        <v>2.33431623092478</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C101" s="2">
+        <v>48.8748924273578</v>
+      </c>
+      <c r="D101" s="2">
+        <v>2.32400509319721</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
     <row r="102" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="103" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="104" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/locais.xlsx
+++ b/locais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arman\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A883B1-82F6-479E-AA67-CC8526350947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6116F02-07DE-4602-9E45-0437E3B38751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="268">
   <si>
     <t>categoria</t>
   </si>
@@ -938,6 +938,12 @@
   </si>
   <si>
     <t>73 Bd Haussmann, 75008 Paris, França</t>
+  </si>
+  <si>
+    <t>Draeger Paris</t>
+  </si>
+  <si>
+    <t>Westfield Forum des Halles, 101 Rue Berger Niveau RER -4, 75001 Paris, França</t>
   </si>
 </sst>
 </file>
@@ -3060,10 +3066,10 @@
         <v>204</v>
       </c>
       <c r="C76" s="2">
-        <v>48.8632227508607</v>
+        <v>48.861576465059997</v>
       </c>
       <c r="D76" s="2">
-        <v>2.3486028944285802</v>
+        <v>2.3473627358828701</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>206</v>
@@ -3599,10 +3605,10 @@
         <v>254</v>
       </c>
       <c r="C98" s="2">
-        <v>48.861846188110803</v>
+        <v>48.861940223559998</v>
       </c>
       <c r="D98" s="2">
-        <v>2.34700921536915</v>
+        <v>2.3469845769120901</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>111</v>
@@ -3695,7 +3701,32 @@
         <v>146</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="102" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C102" s="2">
+        <v>48.862171229824803</v>
+      </c>
+      <c r="D102" s="2">
+        <v>2.3473963224068299</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
     <row r="103" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="104" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="105" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/locais.xlsx
+++ b/locais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arman\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6116F02-07DE-4602-9E45-0437E3B38751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F260A7-11B2-4A20-B9D4-BACAA2A82F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="271">
   <si>
     <t>categoria</t>
   </si>
@@ -944,6 +944,15 @@
   </si>
   <si>
     <t>Westfield Forum des Halles, 101 Rue Berger Niveau RER -4, 75001 Paris, França</t>
+  </si>
+  <si>
+    <t>Saint-Michel Notre-Dame</t>
+  </si>
+  <si>
+    <t>Quai Saint-Michel, 75005 Paris, França</t>
+  </si>
+  <si>
+    <t>Chegada do Massy TGV</t>
   </si>
 </sst>
 </file>
@@ -3727,7 +3736,32 @@
         <v>146</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="103" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C103" s="2">
+        <v>48.853777376863199</v>
+      </c>
+      <c r="D103" s="2">
+        <v>2.3447079577309502</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
     <row r="104" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="105" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="106" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
